--- a/docs/whatsapp-message-volume-model.xlsx
+++ b/docs/whatsapp-message-volume-model.xlsx
@@ -45,9 +45,9 @@
     <definedName name="deals_otp">Inputs!$B$38</definedName>
     <definedName name="deals_registered">Inputs!$B$39</definedName>
     <definedName name="deadline_reminders">Inputs!$B$40</definedName>
-    <definedName name="concierge_estimate">Inputs!$B$41</definedName>
-    <definedName name="concierge_seller">Inputs!$B$42</definedName>
-    <definedName name="concierge_buyer">Inputs!$B$43</definedName>
+    <definedName name="estate_agent_estimate">Inputs!$B$41</definedName>
+    <definedName name="estate_agent_seller">Inputs!$B$42</definedName>
+    <definedName name="estate_agent_buyer">Inputs!$B$43</definedName>
     <definedName name="overhead">Inputs!$B$44</definedName>
     <definedName name="months">Inputs!$B$45</definedName>
     <definedName name="deals_Y1">Inputs!$B$48</definedName>
@@ -646,7 +646,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Charged since 1 Oct 2026 after the free tier below. Covers every scripted-flow reply and every concierge reply.</t>
+          <t>Charged since 1 Oct 2026 after the free tier below. Covers every scripted-flow reply and every WhatsApp estate agent reply.</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Concierge free-text replies per estimate contact</t>
+          <t>WhatsApp estate agent free-text replies per estimate contact</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
@@ -1227,7 +1227,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Concierge free-text replies per listed seller (over the listing's life)</t>
+          <t>WhatsApp estate agent free-text replies per listed seller (over the listing's life)</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
@@ -1247,7 +1247,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Concierge free-text replies per enquiring buyer</t>
+          <t>WhatsApp estate agent free-text replies per enquiring buyer</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
@@ -2087,7 +2087,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Concierge replies — estimate contacts</t>
+          <t>WhatsApp estate agent replies — estimate contacts</t>
         </is>
       </c>
       <c r="B16" s="8">
@@ -2095,7 +2095,7 @@
         <v/>
       </c>
       <c r="C16" s="9">
-        <f>concierge_estimate</f>
+        <f>estate_agent_estimate</f>
         <v/>
       </c>
       <c r="D16" s="9" t="n">
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="9">
-        <f>concierge_estimate</f>
+        <f>estate_agent_estimate</f>
         <v/>
       </c>
       <c r="H16" s="10">
@@ -2140,7 +2140,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Concierge replies — listed sellers</t>
+          <t>WhatsApp estate agent replies — listed sellers</t>
         </is>
       </c>
       <c r="B17" s="8">
@@ -2148,7 +2148,7 @@
         <v/>
       </c>
       <c r="C17" s="9">
-        <f>concierge_seller</f>
+        <f>estate_agent_seller</f>
         <v/>
       </c>
       <c r="D17" s="9" t="n">
@@ -2161,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="9">
-        <f>concierge_seller</f>
+        <f>estate_agent_seller</f>
         <v/>
       </c>
       <c r="H17" s="10">
@@ -2189,7 +2189,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Concierge replies — enquiring buyers</t>
+          <t>WhatsApp estate agent replies — enquiring buyers</t>
         </is>
       </c>
       <c r="B18" s="8">
@@ -2197,7 +2197,7 @@
         <v/>
       </c>
       <c r="C18" s="9">
-        <f>concierge_buyer</f>
+        <f>estate_agent_buyer</f>
         <v/>
       </c>
       <c r="D18" s="9" t="n">
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="9">
-        <f>concierge_buyer</f>
+        <f>estate_agent_buyer</f>
         <v/>
       </c>
       <c r="H18" s="10">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>LOOM report cost (R7.50 each), Property24 subscription (R7,153/month ex VAT at the launch profile), AI concierge inference, e-signature envelopes, SMS fallback, Meta ads spend.</t>
+          <t>LOOM report cost (R7.50 each), Property24 subscription (R7,153/month ex VAT at the launch profile), AI WhatsApp estate agent inference, e-signature envelopes, SMS fallback, Meta ads spend.</t>
         </is>
       </c>
     </row>
